--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/18.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/18.xlsx
@@ -426,13 +426,13 @@
         <v>-21.65526747597563</v>
       </c>
       <c r="E2">
-        <v>-35.64237792496588</v>
+        <v>-32.11178259996674</v>
       </c>
       <c r="F2">
-        <v>-5.980079724699387</v>
+        <v>-4.779073176314051</v>
       </c>
       <c r="G2">
-        <v>-22.84567865171408</v>
+        <v>-17.74090515961471</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.77639736299014</v>
       </c>
       <c r="E3">
-        <v>-35.78701059205986</v>
+        <v>-31.64335724861331</v>
       </c>
       <c r="F3">
-        <v>-5.976769779336118</v>
+        <v>-4.297887889496507</v>
       </c>
       <c r="G3">
-        <v>-22.72277464856864</v>
+        <v>-18.87238175875404</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.83151235485351</v>
       </c>
       <c r="E4">
-        <v>-36.75874639428479</v>
+        <v>-33.01793251313858</v>
       </c>
       <c r="F4">
-        <v>-5.888427495961075</v>
+        <v>-4.768454428151029</v>
       </c>
       <c r="G4">
-        <v>-22.56078468951379</v>
+        <v>-18.55483919644546</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.79092522415156</v>
       </c>
       <c r="E5">
-        <v>-37.52412416445419</v>
+        <v>-32.41945618099587</v>
       </c>
       <c r="F5">
-        <v>-6.031226299091461</v>
+        <v>-4.242378205307396</v>
       </c>
       <c r="G5">
-        <v>-22.89283902819377</v>
+        <v>-18.30021520738349</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.64565417813272</v>
       </c>
       <c r="E6">
-        <v>-36.89615388109954</v>
+        <v>-32.77722600573487</v>
       </c>
       <c r="F6">
-        <v>-5.789034112708095</v>
+        <v>-4.637325162058559</v>
       </c>
       <c r="G6">
-        <v>-22.62968707382264</v>
+        <v>-18.62646119391482</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.39167476162939</v>
       </c>
       <c r="E7">
-        <v>-38.09050720130454</v>
+        <v>-32.82420892356445</v>
       </c>
       <c r="F7">
-        <v>-5.679378315123068</v>
+        <v>-4.636727313075481</v>
       </c>
       <c r="G7">
-        <v>-22.5096069660222</v>
+        <v>-17.33443803357576</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.02875914443593</v>
       </c>
       <c r="E8">
-        <v>-37.12967370025307</v>
+        <v>-34.07622556754612</v>
       </c>
       <c r="F8">
-        <v>-5.991352543405485</v>
+        <v>-4.285294260056932</v>
       </c>
       <c r="G8">
-        <v>-22.75238416787188</v>
+        <v>-17.93472270348411</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.56276291798067</v>
       </c>
       <c r="E9">
-        <v>-37.98046754715515</v>
+        <v>-33.00580752398304</v>
       </c>
       <c r="F9">
-        <v>-5.840244035336788</v>
+        <v>-4.237652426855725</v>
       </c>
       <c r="G9">
-        <v>-22.19894537261699</v>
+        <v>-18.42229653996242</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.00395224131431</v>
       </c>
       <c r="E10">
-        <v>-38.40784681010305</v>
+        <v>-34.62510831659382</v>
       </c>
       <c r="F10">
-        <v>-5.799187251331977</v>
+        <v>-4.149947585111646</v>
       </c>
       <c r="G10">
-        <v>-22.10153091485117</v>
+        <v>-16.3697632714326</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.36639443328812</v>
       </c>
       <c r="E11">
-        <v>-39.07916138242213</v>
+        <v>-34.95513444532482</v>
       </c>
       <c r="F11">
-        <v>-5.660362758196387</v>
+        <v>-4.335230883129611</v>
       </c>
       <c r="G11">
-        <v>-21.6607268104789</v>
+        <v>-17.34112368029232</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.66834169415298</v>
       </c>
       <c r="E12">
-        <v>-38.70427619017114</v>
+        <v>-35.13939805269693</v>
       </c>
       <c r="F12">
-        <v>-5.478680807430131</v>
+        <v>-4.240825381657308</v>
       </c>
       <c r="G12">
-        <v>-21.09233097047758</v>
+        <v>-16.95003900410159</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.9225515413437</v>
       </c>
       <c r="E13">
-        <v>-39.87460595576545</v>
+        <v>-36.20589670200637</v>
       </c>
       <c r="F13">
-        <v>-5.64746426536809</v>
+        <v>-4.343546131038626</v>
       </c>
       <c r="G13">
-        <v>-21.20640409339702</v>
+        <v>-16.6251867572423</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.15825462920244</v>
       </c>
       <c r="E14">
-        <v>-40.70296347819653</v>
+        <v>-35.67977632755822</v>
       </c>
       <c r="F14">
-        <v>-5.826970996059489</v>
+        <v>-4.544139114141144</v>
       </c>
       <c r="G14">
-        <v>-20.59922355713037</v>
+        <v>-17.13775355726935</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.39334140224078</v>
       </c>
       <c r="E15">
-        <v>-40.97586970003178</v>
+        <v>-36.8761176478526</v>
       </c>
       <c r="F15">
-        <v>-5.53471549013021</v>
+        <v>-4.492645708153588</v>
       </c>
       <c r="G15">
-        <v>-20.18976204265115</v>
+        <v>-15.4842552400428</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.64925360038547</v>
       </c>
       <c r="E16">
-        <v>-40.95105139823274</v>
+        <v>-37.89475711961197</v>
       </c>
       <c r="F16">
-        <v>-5.682646292279578</v>
+        <v>-3.995748474948969</v>
       </c>
       <c r="G16">
-        <v>-20.02494156716023</v>
+        <v>-16.08079899349178</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.94241342406586</v>
       </c>
       <c r="E17">
-        <v>-41.73365321929032</v>
+        <v>-38.18921661348673</v>
       </c>
       <c r="F17">
-        <v>-5.554470637719401</v>
+        <v>-3.973513243896199</v>
       </c>
       <c r="G17">
-        <v>-19.71725615419482</v>
+        <v>-16.11905896828913</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.28683165235819</v>
       </c>
       <c r="E18">
-        <v>-41.79886324500077</v>
+        <v>-37.65469818399136</v>
       </c>
       <c r="F18">
-        <v>-5.221946241478242</v>
+        <v>-3.935924775846201</v>
       </c>
       <c r="G18">
-        <v>-19.66111592293986</v>
+        <v>-15.16153332923803</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.69344521684228</v>
       </c>
       <c r="E19">
-        <v>-42.82417542321046</v>
+        <v>-37.47244295484165</v>
       </c>
       <c r="F19">
-        <v>-5.286665175565633</v>
+        <v>-3.975577604556974</v>
       </c>
       <c r="G19">
-        <v>-19.08196577575422</v>
+        <v>-14.46978656244347</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.16436994201225</v>
       </c>
       <c r="E20">
-        <v>-42.88623136677457</v>
+        <v>-38.82830430053022</v>
       </c>
       <c r="F20">
-        <v>-5.110222915820609</v>
+        <v>-3.39287360114793</v>
       </c>
       <c r="G20">
-        <v>-18.94095970960004</v>
+        <v>-14.20531038985663</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.7093064039926</v>
       </c>
       <c r="E21">
-        <v>-43.23749151012753</v>
+        <v>-40.05212666534014</v>
       </c>
       <c r="F21">
-        <v>-5.368223654651891</v>
+        <v>-3.455061773182449</v>
       </c>
       <c r="G21">
-        <v>-19.35405785835415</v>
+        <v>-13.71769682683184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.32580477979873</v>
       </c>
       <c r="E22">
-        <v>-43.24919535120036</v>
+        <v>-38.6304530068981</v>
       </c>
       <c r="F22">
-        <v>-5.052634617617484</v>
+        <v>-2.816659624580357</v>
       </c>
       <c r="G22">
-        <v>-18.5770513017412</v>
+        <v>-13.58564578636139</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.01373944725652</v>
       </c>
       <c r="E23">
-        <v>-43.14016554675468</v>
+        <v>-39.16102487129579</v>
       </c>
       <c r="F23">
-        <v>-4.815933931495904</v>
+        <v>-3.364149135106647</v>
       </c>
       <c r="G23">
-        <v>-18.78163970552262</v>
+        <v>-14.10498430728902</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.76752877164093</v>
       </c>
       <c r="E24">
-        <v>-44.58040594862817</v>
+        <v>-40.9668489798085</v>
       </c>
       <c r="F24">
-        <v>-4.858399421912497</v>
+        <v>-3.077307527849297</v>
       </c>
       <c r="G24">
-        <v>-18.55219903637789</v>
+        <v>-13.72947574786057</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.58003637195802</v>
       </c>
       <c r="E25">
-        <v>-44.90274725696815</v>
+        <v>-40.00917408937739</v>
       </c>
       <c r="F25">
-        <v>-4.696484496529799</v>
+        <v>-2.931896401811393</v>
       </c>
       <c r="G25">
-        <v>-18.38799928817557</v>
+        <v>-13.94151618965089</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.44328851132597</v>
       </c>
       <c r="E26">
-        <v>-44.42998362751538</v>
+        <v>-41.63648348827073</v>
       </c>
       <c r="F26">
-        <v>-4.550992601490208</v>
+        <v>-3.589891368146344</v>
       </c>
       <c r="G26">
-        <v>-18.86691273752317</v>
+        <v>-14.07513477343418</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.34572473845616</v>
       </c>
       <c r="E27">
-        <v>-44.96720329175633</v>
+        <v>-40.54911083802293</v>
       </c>
       <c r="F27">
-        <v>-4.733135410677857</v>
+        <v>-3.336574439559973</v>
       </c>
       <c r="G27">
-        <v>-18.23588468646437</v>
+        <v>-13.92157180804955</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.28182012328407</v>
       </c>
       <c r="E28">
-        <v>-44.22007300760083</v>
+        <v>-41.16765283849362</v>
       </c>
       <c r="F28">
-        <v>-4.578998856898839</v>
+        <v>-2.912700302410351</v>
       </c>
       <c r="G28">
-        <v>-18.63015907328219</v>
+        <v>-13.64338170056628</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.24139066246145</v>
       </c>
       <c r="E29">
-        <v>-44.62252981384751</v>
+        <v>-39.77192280764153</v>
       </c>
       <c r="F29">
-        <v>-4.816327482415891</v>
+        <v>-2.978237220603067</v>
       </c>
       <c r="G29">
-        <v>-18.65611043976453</v>
+        <v>-13.62418715752958</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.22021024249502</v>
       </c>
       <c r="E30">
-        <v>-44.42405132656533</v>
+        <v>-40.39108068057726</v>
       </c>
       <c r="F30">
-        <v>-4.814581446644119</v>
+        <v>-3.080427428502713</v>
       </c>
       <c r="G30">
-        <v>-18.52609869534627</v>
+        <v>-14.1449111417654</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.21268739563049</v>
       </c>
       <c r="E31">
-        <v>-44.13018959125959</v>
+        <v>-41.30486333668903</v>
       </c>
       <c r="F31">
-        <v>-4.843508627042578</v>
+        <v>-3.182520238488559</v>
       </c>
       <c r="G31">
-        <v>-18.70865045274553</v>
+        <v>-13.76943403251957</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.21467945739259</v>
       </c>
       <c r="E32">
-        <v>-44.75290684476535</v>
+        <v>-40.16495585947825</v>
       </c>
       <c r="F32">
-        <v>-4.793123023342872</v>
+        <v>-3.089379326189734</v>
       </c>
       <c r="G32">
-        <v>-18.7185572602718</v>
+        <v>-14.38209848747202</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.22385993840243</v>
       </c>
       <c r="E33">
-        <v>-44.63806700816784</v>
+        <v>-39.63663011818837</v>
       </c>
       <c r="F33">
-        <v>-4.783488548406297</v>
+        <v>-3.082440318721236</v>
       </c>
       <c r="G33">
-        <v>-18.63168523477579</v>
+        <v>-15.03373799505831</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.23788275332128</v>
       </c>
       <c r="E34">
-        <v>-43.59042945310034</v>
+        <v>-38.44792154083392</v>
       </c>
       <c r="F34">
-        <v>-4.706185487114824</v>
+        <v>-2.935295826558884</v>
       </c>
       <c r="G34">
-        <v>-19.11061854739661</v>
+        <v>-14.94982559727441</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.25705647520071</v>
       </c>
       <c r="E35">
-        <v>-43.14710316893443</v>
+        <v>-38.59413464535658</v>
       </c>
       <c r="F35">
-        <v>-4.55263807193635</v>
+        <v>-2.969377177859141</v>
       </c>
       <c r="G35">
-        <v>-19.13005144971213</v>
+        <v>-14.52162970558845</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.28175972827571</v>
       </c>
       <c r="E36">
-        <v>-43.43055167825954</v>
+        <v>-39.19035806168047</v>
       </c>
       <c r="F36">
-        <v>-4.610272297611022</v>
+        <v>-3.133774562264291</v>
       </c>
       <c r="G36">
-        <v>-19.23142863048847</v>
+        <v>-14.74043524718827</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.31365144225849</v>
       </c>
       <c r="E37">
-        <v>-42.98071118423359</v>
+        <v>-38.82254408159247</v>
       </c>
       <c r="F37">
-        <v>-4.554557523505863</v>
+        <v>-2.605486694109746</v>
       </c>
       <c r="G37">
-        <v>-18.743568431821</v>
+        <v>-14.55776762069514</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.35425456486036</v>
       </c>
       <c r="E38">
-        <v>-42.39136878416436</v>
+        <v>-38.21476626383801</v>
       </c>
       <c r="F38">
-        <v>-4.604778421790362</v>
+        <v>-2.6261714770713</v>
       </c>
       <c r="G38">
-        <v>-19.28832201085361</v>
+        <v>-14.62640847190639</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.40348218562064</v>
       </c>
       <c r="E39">
-        <v>-42.35669425868763</v>
+        <v>-38.29067707362859</v>
       </c>
       <c r="F39">
-        <v>-4.38476128563498</v>
+        <v>-2.923359435074217</v>
       </c>
       <c r="G39">
-        <v>-19.41108366054086</v>
+        <v>-15.42585556145729</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.46049438027194</v>
       </c>
       <c r="E40">
-        <v>-41.69294223796136</v>
+        <v>-36.84057365536639</v>
       </c>
       <c r="F40">
-        <v>-4.656832459671985</v>
+        <v>-2.798782752206877</v>
       </c>
       <c r="G40">
-        <v>-19.02564677504014</v>
+        <v>-14.87487650153808</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.52344644731036</v>
       </c>
       <c r="E41">
-        <v>-41.97443671075216</v>
+        <v>-36.27871909252372</v>
       </c>
       <c r="F41">
-        <v>-4.62734781479129</v>
+        <v>-2.838053907792029</v>
       </c>
       <c r="G41">
-        <v>-19.48905197380901</v>
+        <v>-14.76643627185371</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.58885235888203</v>
       </c>
       <c r="E42">
-        <v>-41.04861963496501</v>
+        <v>-36.22394040668993</v>
       </c>
       <c r="F42">
-        <v>-4.433599608655301</v>
+        <v>-2.542306330319204</v>
       </c>
       <c r="G42">
-        <v>-18.87549698210649</v>
+        <v>-15.63527074063497</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.65715961858457</v>
       </c>
       <c r="E43">
-        <v>-41.35723287435074</v>
+        <v>-35.70942877536045</v>
       </c>
       <c r="F43">
-        <v>-4.265980174565191</v>
+        <v>-2.755186495766659</v>
       </c>
       <c r="G43">
-        <v>-19.43981257473066</v>
+        <v>-15.58950244855454</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.72603626762942</v>
       </c>
       <c r="E44">
-        <v>-40.66307667913697</v>
+        <v>-36.19030969447197</v>
       </c>
       <c r="F44">
-        <v>-4.514176981926945</v>
+        <v>-2.927022546856628</v>
       </c>
       <c r="G44">
-        <v>-19.42668295112191</v>
+        <v>-16.04445416928889</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.7968141814085</v>
       </c>
       <c r="E45">
-        <v>-40.20607213923089</v>
+        <v>-34.97579334374782</v>
       </c>
       <c r="F45">
-        <v>-4.368987574717202</v>
+        <v>-2.772669817220153</v>
       </c>
       <c r="G45">
-        <v>-19.61759714655337</v>
+        <v>-16.29157149634055</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.86898749853423</v>
       </c>
       <c r="E46">
-        <v>-40.83887204011474</v>
+        <v>-34.29101561820394</v>
       </c>
       <c r="F46">
-        <v>-4.272741806971159</v>
+        <v>-2.836270654931244</v>
       </c>
       <c r="G46">
-        <v>-19.55733197555648</v>
+        <v>-15.87423253875064</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.94237657716372</v>
       </c>
       <c r="E47">
-        <v>-39.13890780424232</v>
+        <v>-34.55450034986622</v>
       </c>
       <c r="F47">
-        <v>-4.386561167407876</v>
+        <v>-2.776199897705668</v>
       </c>
       <c r="G47">
-        <v>-19.86978788464397</v>
+        <v>-16.22117109017518</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.01681617089905</v>
       </c>
       <c r="E48">
-        <v>-39.57519910403732</v>
+        <v>-33.81311217075246</v>
       </c>
       <c r="F48">
-        <v>-4.19393739247185</v>
+        <v>-2.347809031285213</v>
       </c>
       <c r="G48">
-        <v>-19.71791826330267</v>
+        <v>-15.81776456348729</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.08853763160157</v>
       </c>
       <c r="E49">
-        <v>-38.67764649876904</v>
+        <v>-34.18765772745287</v>
       </c>
       <c r="F49">
-        <v>-4.15985683302455</v>
+        <v>-2.471552684841032</v>
       </c>
       <c r="G49">
-        <v>-19.78354320752765</v>
+        <v>-15.68390762042517</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.16010954670851</v>
       </c>
       <c r="E50">
-        <v>-38.29425683233165</v>
+        <v>-31.92854469195737</v>
       </c>
       <c r="F50">
-        <v>-4.272684793558203</v>
+        <v>-2.693126603911292</v>
       </c>
       <c r="G50">
-        <v>-19.88589037814699</v>
+        <v>-16.29412227167856</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.22751272438855</v>
       </c>
       <c r="E51">
-        <v>-38.51512183087075</v>
+        <v>-32.8608442782865</v>
       </c>
       <c r="F51">
-        <v>-4.002267800349875</v>
+        <v>-2.44532809858727</v>
       </c>
       <c r="G51">
-        <v>-19.92017935356999</v>
+        <v>-15.94520732456707</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.29254301555663</v>
       </c>
       <c r="E52">
-        <v>-38.33003177699224</v>
+        <v>-32.92205113297418</v>
       </c>
       <c r="F52">
-        <v>-3.914386375396225</v>
+        <v>-2.5609489245028</v>
       </c>
       <c r="G52">
-        <v>-20.00767541690016</v>
+        <v>-16.25341083790937</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.35392919740967</v>
       </c>
       <c r="E53">
-        <v>-37.41508077458649</v>
+        <v>-31.9452728749417</v>
       </c>
       <c r="F53">
-        <v>-4.510530499056646</v>
+        <v>-2.364181383039026</v>
       </c>
       <c r="G53">
-        <v>-20.67736401876655</v>
+        <v>-16.12976361729037</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.41034160069957</v>
       </c>
       <c r="E54">
-        <v>-37.8529751541802</v>
+        <v>-31.21871091972904</v>
       </c>
       <c r="F54">
-        <v>-4.114740218905512</v>
+        <v>-2.639326530257898</v>
       </c>
       <c r="G54">
-        <v>-20.11146598537462</v>
+        <v>-15.61122459311047</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.46047469925653</v>
       </c>
       <c r="E55">
-        <v>-37.43744690771038</v>
+        <v>-30.22327761302197</v>
       </c>
       <c r="F55">
-        <v>-4.119757399245624</v>
+        <v>-3.014407480005788</v>
       </c>
       <c r="G55">
-        <v>-20.24001446866452</v>
+        <v>-16.39847728816747</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.50015049870027</v>
       </c>
       <c r="E56">
-        <v>-36.6601569866638</v>
+        <v>-30.95091734504846</v>
       </c>
       <c r="F56">
-        <v>-4.238927310117654</v>
+        <v>-2.508884592532728</v>
       </c>
       <c r="G56">
-        <v>-20.11988470268098</v>
+        <v>-15.99495323711293</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.53102955093117</v>
       </c>
       <c r="E57">
-        <v>-36.37449405354894</v>
+        <v>-30.59895075975029</v>
       </c>
       <c r="F57">
-        <v>-4.369270266223109</v>
+        <v>-2.716402329750505</v>
       </c>
       <c r="G57">
-        <v>-20.54489253901262</v>
+        <v>-16.70714262261249</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.54838794197539</v>
       </c>
       <c r="E58">
-        <v>-36.06784164340853</v>
+        <v>-30.00302622271091</v>
       </c>
       <c r="F58">
-        <v>-4.443861231134392</v>
+        <v>-2.79077711880433</v>
       </c>
       <c r="G58">
-        <v>-20.6874793906618</v>
+        <v>-16.06192557337239</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.55538835441962</v>
       </c>
       <c r="E59">
-        <v>-36.075793643766</v>
+        <v>-30.23282137199314</v>
       </c>
       <c r="F59">
-        <v>-4.208156696033623</v>
+        <v>-3.131269931359023</v>
       </c>
       <c r="G59">
-        <v>-20.57220950552992</v>
+        <v>-16.07798502978339</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.55195655181107</v>
       </c>
       <c r="E60">
-        <v>-36.25419740577218</v>
+        <v>-29.20242371747285</v>
       </c>
       <c r="F60">
-        <v>-4.619950324460272</v>
+        <v>-3.167992904126233</v>
       </c>
       <c r="G60">
-        <v>-20.45841446843578</v>
+        <v>-16.81318932787197</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.53842815489763</v>
       </c>
       <c r="E61">
-        <v>-35.4072369121176</v>
+        <v>-29.20048100212356</v>
       </c>
       <c r="F61">
-        <v>-4.426548158066807</v>
+        <v>-3.053684970414602</v>
       </c>
       <c r="G61">
-        <v>-20.45542835635936</v>
+        <v>-16.20600217051424</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.51573146227466</v>
       </c>
       <c r="E62">
-        <v>-35.71085524467286</v>
+        <v>-28.54128915472301</v>
       </c>
       <c r="F62">
-        <v>-4.614818325441291</v>
+        <v>-3.244103434863379</v>
       </c>
       <c r="G62">
-        <v>-20.76466310463714</v>
+        <v>-16.61043496631931</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.48313274022986</v>
       </c>
       <c r="E63">
-        <v>-34.48012016429024</v>
+        <v>-29.029531108334</v>
       </c>
       <c r="F63">
-        <v>-4.686652058353793</v>
+        <v>-3.309856528913552</v>
       </c>
       <c r="G63">
-        <v>-20.54460783209624</v>
+        <v>-16.5650639397036</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.44375954380223</v>
       </c>
       <c r="E64">
-        <v>-34.95674205359754</v>
+        <v>-29.03448525889839</v>
       </c>
       <c r="F64">
-        <v>-4.586321913051831</v>
+        <v>-3.398528223119007</v>
       </c>
       <c r="G64">
-        <v>-20.92725061716182</v>
+        <v>-16.56265717309654</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.39763798571408</v>
       </c>
       <c r="E65">
-        <v>-34.7739275579079</v>
+        <v>-28.67812605381279</v>
       </c>
       <c r="F65">
-        <v>-4.730366300884711</v>
+        <v>-3.157870647767702</v>
       </c>
       <c r="G65">
-        <v>-20.21061847954856</v>
+        <v>-16.91130396601935</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.34962809008341</v>
       </c>
       <c r="E66">
-        <v>-35.08789345357069</v>
+        <v>-28.32817463944804</v>
       </c>
       <c r="F66">
-        <v>-4.735641625289039</v>
+        <v>-3.083006493586006</v>
       </c>
       <c r="G66">
-        <v>-20.80813387811331</v>
+        <v>-16.54590912321337</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.30256266132739</v>
       </c>
       <c r="E67">
-        <v>-34.28962990515759</v>
+        <v>-28.70291492053077</v>
       </c>
       <c r="F67">
-        <v>-4.645859753236862</v>
+        <v>-3.434989092557212</v>
       </c>
       <c r="G67">
-        <v>-20.72010812749685</v>
+        <v>-17.06932127042707</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.25861385457108</v>
       </c>
       <c r="E68">
-        <v>-35.17211627740235</v>
+        <v>-27.95996441788436</v>
       </c>
       <c r="F68">
-        <v>-4.668741136303131</v>
+        <v>-3.568161339280599</v>
       </c>
       <c r="G68">
-        <v>-20.83393130422808</v>
+        <v>-16.1650921040127</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.21964355541625</v>
       </c>
       <c r="E69">
-        <v>-33.95502548920483</v>
+        <v>-28.11700736799636</v>
       </c>
       <c r="F69">
-        <v>-4.761653994950133</v>
+        <v>-3.908186958590237</v>
       </c>
       <c r="G69">
-        <v>-21.43096667368963</v>
+        <v>-16.5797329669881</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.18575074203032</v>
       </c>
       <c r="E70">
-        <v>-35.46665275533523</v>
+        <v>-28.75938499140642</v>
       </c>
       <c r="F70">
-        <v>-4.840428319037049</v>
+        <v>-3.557366799760964</v>
       </c>
       <c r="G70">
-        <v>-20.50708445368137</v>
+        <v>-16.74602001415293</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.15690609829243</v>
       </c>
       <c r="E71">
-        <v>-34.6952317366026</v>
+        <v>-28.80349685671514</v>
       </c>
       <c r="F71">
-        <v>-4.97438054092379</v>
+        <v>-3.666304386713339</v>
       </c>
       <c r="G71">
-        <v>-20.19221350162298</v>
+        <v>-16.21923111048917</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.13396154057324</v>
       </c>
       <c r="E72">
-        <v>-34.42990391601919</v>
+        <v>-26.93925090502947</v>
       </c>
       <c r="F72">
-        <v>-4.980945793796244</v>
+        <v>-3.905694205479335</v>
       </c>
       <c r="G72">
-        <v>-20.22637502104272</v>
+        <v>-16.24743199266545</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.11672445300508</v>
       </c>
       <c r="E73">
-        <v>-34.28332853357591</v>
+        <v>-28.60961929902475</v>
       </c>
       <c r="F73">
-        <v>-5.082032950525787</v>
+        <v>-3.730399340670047</v>
       </c>
       <c r="G73">
-        <v>-20.7577639277333</v>
+        <v>-16.17074982633931</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.10589386241533</v>
       </c>
       <c r="E74">
-        <v>-35.23341823004418</v>
+        <v>-29.06244858589575</v>
       </c>
       <c r="F74">
-        <v>-4.875698241626843</v>
+        <v>-4.176933933910735</v>
       </c>
       <c r="G74">
-        <v>-20.27959369585927</v>
+        <v>-15.20215537827766</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.10004102966587</v>
       </c>
       <c r="E75">
-        <v>-35.22992677658426</v>
+        <v>-29.03193119955806</v>
       </c>
       <c r="F75">
-        <v>-5.062351445261663</v>
+        <v>-3.880002536266119</v>
       </c>
       <c r="G75">
-        <v>-20.22125691763901</v>
+        <v>-16.07222633581783</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.09734028069547</v>
       </c>
       <c r="E76">
-        <v>-35.5622148780821</v>
+        <v>-29.77268539231076</v>
       </c>
       <c r="F76">
-        <v>-5.298492291342135</v>
+        <v>-3.890120833359862</v>
       </c>
       <c r="G76">
-        <v>-20.17590244375099</v>
+        <v>-15.77256402996685</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.09535481724297</v>
       </c>
       <c r="E77">
-        <v>-35.0443272693799</v>
+        <v>-29.14329543235469</v>
       </c>
       <c r="F77">
-        <v>-5.467479255490228</v>
+        <v>-3.555779134580736</v>
       </c>
       <c r="G77">
-        <v>-19.3713306297053</v>
+        <v>-16.20667752180425</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.08852509735757</v>
       </c>
       <c r="E78">
-        <v>-35.66209716503228</v>
+        <v>-29.14512040737979</v>
       </c>
       <c r="F78">
-        <v>-5.483041541668293</v>
+        <v>-4.360190880209895</v>
       </c>
       <c r="G78">
-        <v>-19.52373655942396</v>
+        <v>-15.44374409427874</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.0775464119544</v>
       </c>
       <c r="E79">
-        <v>-35.04654848588066</v>
+        <v>-30.4255011483085</v>
       </c>
       <c r="F79">
-        <v>-5.373059500664685</v>
+        <v>-4.53416018316796</v>
       </c>
       <c r="G79">
-        <v>-20.04326212617455</v>
+        <v>-15.4875972357647</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.05811593508429</v>
       </c>
       <c r="E80">
-        <v>-35.90876540846709</v>
+        <v>-30.02097709367732</v>
       </c>
       <c r="F80">
-        <v>-5.693484383711887</v>
+        <v>-3.931591756461559</v>
       </c>
       <c r="G80">
-        <v>-19.40721528807823</v>
+        <v>-15.70208251543577</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.02997739532673</v>
       </c>
       <c r="E81">
-        <v>-35.93424486747124</v>
+        <v>-31.43279226420466</v>
       </c>
       <c r="F81">
-        <v>-5.616951795348276</v>
+        <v>-4.493204756341738</v>
       </c>
       <c r="G81">
-        <v>-19.25666491913433</v>
+        <v>-15.19190923983361</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.99078560845737</v>
       </c>
       <c r="E82">
-        <v>-37.31307463332671</v>
+        <v>-31.20651347498939</v>
       </c>
       <c r="F82">
-        <v>-5.581413434605815</v>
+        <v>-4.755225732639364</v>
       </c>
       <c r="G82">
-        <v>-19.63585314992968</v>
+        <v>-14.69916433122295</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.93835264612398</v>
       </c>
       <c r="E83">
-        <v>-37.242398739489</v>
+        <v>-30.6172548516893</v>
       </c>
       <c r="F83">
-        <v>-5.668312170038935</v>
+        <v>-4.497938453322987</v>
       </c>
       <c r="G83">
-        <v>-19.42857658317038</v>
+        <v>-14.69347515871371</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.87099104450142</v>
       </c>
       <c r="E84">
-        <v>-37.37128363822131</v>
+        <v>-33.16616984554266</v>
       </c>
       <c r="F84">
-        <v>-5.601026048662617</v>
+        <v>-4.597546428727508</v>
       </c>
       <c r="G84">
-        <v>-19.38260634781205</v>
+        <v>-14.69041952518096</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.78390617653901</v>
       </c>
       <c r="E85">
-        <v>-37.79872629980532</v>
+        <v>-32.52460055474297</v>
       </c>
       <c r="F85">
-        <v>-5.392314989037557</v>
+        <v>-4.239254345389192</v>
       </c>
       <c r="G85">
-        <v>-19.07629977706376</v>
+        <v>-14.67794207904345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.68000042932861</v>
       </c>
       <c r="E86">
-        <v>-38.86147763687341</v>
+        <v>-33.60857232101101</v>
       </c>
       <c r="F86">
-        <v>-5.686939719016333</v>
+        <v>-4.896484381766985</v>
       </c>
       <c r="G86">
-        <v>-19.70739072848779</v>
+        <v>-14.78077589985706</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.55661158217243</v>
       </c>
       <c r="E87">
-        <v>-39.32145738420252</v>
+        <v>-33.7491972886082</v>
       </c>
       <c r="F87">
-        <v>-5.525511783202633</v>
+        <v>-4.380498741163574</v>
       </c>
       <c r="G87">
-        <v>-19.50127947375831</v>
+        <v>-15.1300699044328</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.41662397123729</v>
       </c>
       <c r="E88">
-        <v>-39.84237227777886</v>
+        <v>-35.11181511751621</v>
       </c>
       <c r="F88">
-        <v>-5.814978383014824</v>
+        <v>-4.397692244434543</v>
       </c>
       <c r="G88">
-        <v>-18.87864034509603</v>
+        <v>-14.18907547453204</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.26081247537307</v>
       </c>
       <c r="E89">
-        <v>-40.99513835693442</v>
+        <v>-35.90729139017759</v>
       </c>
       <c r="F89">
-        <v>-5.669948930102541</v>
+        <v>-4.462099980309549</v>
       </c>
       <c r="G89">
-        <v>-18.88062170660129</v>
+        <v>-13.99103864037284</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.09036098092376</v>
       </c>
       <c r="E90">
-        <v>-41.81939534615155</v>
+        <v>-37.07263304165245</v>
       </c>
       <c r="F90">
-        <v>-5.971079523981945</v>
+        <v>-4.799236128176468</v>
       </c>
       <c r="G90">
-        <v>-18.57673017882389</v>
+        <v>-14.82826567561791</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.9071014057184</v>
       </c>
       <c r="E91">
-        <v>-42.66423198549654</v>
+        <v>-37.21889595938919</v>
       </c>
       <c r="F91">
-        <v>-5.811679523592964</v>
+        <v>-5.071732527251768</v>
       </c>
       <c r="G91">
-        <v>-18.99063775596235</v>
+        <v>-14.58667861488959</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.71069112896212</v>
       </c>
       <c r="E92">
-        <v>-43.57239027689079</v>
+        <v>-39.67624747304448</v>
       </c>
       <c r="F92">
-        <v>-5.87682051530682</v>
+        <v>-4.617989696536958</v>
       </c>
       <c r="G92">
-        <v>-19.356300752957</v>
+        <v>-13.71896145522784</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.50699647461391</v>
       </c>
       <c r="E93">
-        <v>-43.99212547571373</v>
+        <v>-40.5757767572171</v>
       </c>
       <c r="F93">
-        <v>-5.830014878828965</v>
+        <v>-4.939754394788622</v>
       </c>
       <c r="G93">
-        <v>-19.36227463238262</v>
+        <v>-15.19926527202187</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.2972033148548</v>
       </c>
       <c r="E94">
-        <v>-45.29991933404789</v>
+        <v>-41.42256064038539</v>
       </c>
       <c r="F94">
-        <v>-6.023071005479906</v>
+        <v>-4.731554872174248</v>
       </c>
       <c r="G94">
-        <v>-19.21246582563952</v>
+        <v>-14.53116738728709</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.08787573866377</v>
       </c>
       <c r="E95">
-        <v>-46.34787614653292</v>
+        <v>-42.51207752307582</v>
       </c>
       <c r="F95">
-        <v>-6.031882745193411</v>
+        <v>-5.312527093164759</v>
       </c>
       <c r="G95">
-        <v>-19.32389547794585</v>
+        <v>-14.49863962209098</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.882339293085829</v>
       </c>
       <c r="E96">
-        <v>-48.05897137151619</v>
+        <v>-44.3818799123689</v>
       </c>
       <c r="F96">
-        <v>-6.232904516672535</v>
+        <v>-5.251928961869342</v>
       </c>
       <c r="G96">
-        <v>-19.70706960557049</v>
+        <v>-15.72916443321978</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.68361373305569</v>
       </c>
       <c r="E97">
-        <v>-48.26591810519271</v>
+        <v>-45.75510569163988</v>
       </c>
       <c r="F97">
-        <v>-6.176992571180903</v>
+        <v>-5.506573827865808</v>
       </c>
       <c r="G97">
-        <v>-19.62875202974795</v>
+        <v>-14.382939366039</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.493228113327701</v>
       </c>
       <c r="E98">
-        <v>-50.33795987943135</v>
+        <v>-47.30524310073152</v>
       </c>
       <c r="F98">
-        <v>-6.358220790202385</v>
+        <v>-5.203666315949282</v>
       </c>
       <c r="G98">
-        <v>-20.1099894820641</v>
+        <v>-14.80935418422482</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.310859141150667</v>
       </c>
       <c r="E99">
-        <v>-51.726340196969</v>
+        <v>-49.28803770922698</v>
       </c>
       <c r="F99">
-        <v>-6.213746030286985</v>
+        <v>-5.321110779226441</v>
       </c>
       <c r="G99">
-        <v>-19.36185915891744</v>
+        <v>-15.73287224422376</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.136380059326678</v>
       </c>
       <c r="E100">
-        <v>-52.83333472509203</v>
+        <v>-50.03787941719457</v>
       </c>
       <c r="F100">
-        <v>-5.972129521003881</v>
+        <v>-5.507809910332809</v>
       </c>
       <c r="G100">
-        <v>-19.33407706075188</v>
+        <v>-15.74671694566899</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.970393126466222</v>
       </c>
       <c r="E101">
-        <v>-54.34330570185413</v>
+        <v>-52.31723473150436</v>
       </c>
       <c r="F101">
-        <v>-6.155789124532042</v>
+        <v>-5.297578493028926</v>
       </c>
       <c r="G101">
-        <v>-20.24949090527068</v>
+        <v>-15.66031170709401</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.810233288245989</v>
       </c>
       <c r="E102">
-        <v>-55.60820245803212</v>
+        <v>-53.06472163298795</v>
       </c>
       <c r="F102">
-        <v>-6.177276450466245</v>
+        <v>-5.433444623514476</v>
       </c>
       <c r="G102">
-        <v>-19.90818193653567</v>
+        <v>-15.5229108250321</v>
       </c>
     </row>
   </sheetData>
